--- a/FRIDAY SUBMISSION.xlsx
+++ b/FRIDAY SUBMISSION.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="471">
   <si>
     <t>Application_Name</t>
   </si>
@@ -1383,6 +1383,66 @@
   </si>
   <si>
     <t>1. CLEAR LN FIELD 2. CLICK UPDATE</t>
+  </si>
+  <si>
+    <t>PREPARED BY</t>
+  </si>
+  <si>
+    <t>Ujjwal Kumar</t>
+  </si>
+  <si>
+    <t>REVIEWED BY</t>
+  </si>
+  <si>
+    <t>Rehna Rajendran</t>
+  </si>
+  <si>
+    <t>APPROVED BY</t>
+  </si>
+  <si>
+    <t>TEST MANAGER</t>
+  </si>
+  <si>
+    <t>EXECUTION DATE</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>TEST ENVIRONMENT</t>
+  </si>
+  <si>
+    <t>QA / STAGING</t>
+  </si>
+  <si>
+    <t>BUILD VERSION</t>
+  </si>
+  <si>
+    <t>v1.0.0</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASES</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>DEFECT ID REFERENCE</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t>ALL CRITICAL TEST CASES COVERED</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1764,7 @@
     <col customWidth="1" min="2" max="2" width="55.13"/>
     <col customWidth="1" min="3" max="3" width="38.75"/>
     <col customWidth="1" min="4" max="4" width="32.88"/>
-    <col customWidth="1" min="5" max="5" width="90.88"/>
+    <col customWidth="1" min="5" max="5" width="70.25"/>
     <col customWidth="1" min="6" max="6" width="39.75"/>
     <col customWidth="1" min="7" max="7" width="105.38"/>
     <col customWidth="1" min="8" max="8" width="33.38"/>
@@ -5369,13 +5429,13 @@
       <c r="Z89" s="4"/>
     </row>
     <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="4"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="11"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -5397,13 +5457,13 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="4"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="11"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
@@ -5425,13 +5485,16 @@
       <c r="Z91" s="4"/>
     </row>
     <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="4"/>
+      <c r="A92" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="11"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
@@ -5453,13 +5516,16 @@
       <c r="Z92" s="4"/>
     </row>
     <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="4"/>
+      <c r="A93" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="11"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -5481,9 +5547,12 @@
       <c r="Z93" s="4"/>
     </row>
     <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
+      <c r="A94" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>456</v>
+      </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="15"/>
@@ -5511,7 +5580,6 @@
     <row r="95">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="15"/>
@@ -5537,9 +5605,12 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
+      <c r="A96" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>458</v>
+      </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="15"/>
@@ -5565,9 +5636,12 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
+      <c r="A97" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>460</v>
+      </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="15"/>
@@ -5593,9 +5667,12 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
+      <c r="A98" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>462</v>
+      </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="15"/>
@@ -5623,7 +5700,6 @@
     <row r="99">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="15"/>
@@ -5649,9 +5725,12 @@
       <c r="Z99" s="4"/>
     </row>
     <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
+      <c r="A100" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B100" s="11">
+        <v>80.0</v>
+      </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="15"/>
@@ -5677,10 +5756,12 @@
       <c r="Z100" s="4"/>
     </row>
     <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+      <c r="A101" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>465</v>
+      </c>
       <c r="E101" s="4"/>
       <c r="F101" s="15"/>
       <c r="G101" s="4"/>
@@ -5705,10 +5786,12 @@
       <c r="Z101" s="4"/>
     </row>
     <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
+      <c r="A102" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>465</v>
+      </c>
       <c r="E102" s="4"/>
       <c r="F102" s="15"/>
       <c r="G102" s="4"/>
@@ -5733,10 +5816,12 @@
       <c r="Z102" s="4"/>
     </row>
     <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
+      <c r="A103" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>465</v>
+      </c>
       <c r="E103" s="4"/>
       <c r="F103" s="15"/>
       <c r="G103" s="4"/>
@@ -5763,8 +5848,6 @@
     <row r="104">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="15"/>
       <c r="G104" s="4"/>
@@ -5789,10 +5872,10 @@
       <c r="Z104" s="4"/>
     </row>
     <row r="105">
-      <c r="A105" s="4"/>
+      <c r="A105" s="11" t="s">
+        <v>468</v>
+      </c>
       <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="15"/>
       <c r="G105" s="4"/>
@@ -5817,10 +5900,13 @@
       <c r="Z105" s="4"/>
     </row>
     <row r="106">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
+      <c r="A106" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>470</v>
+      </c>
       <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="15"/>
       <c r="G106" s="4"/>
@@ -5848,7 +5934,6 @@
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="15"/>
       <c r="G107" s="4"/>
@@ -30876,6 +30961,62 @@
       <c r="Y1000" s="4"/>
       <c r="Z1000" s="4"/>
     </row>
+    <row r="1001">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="4"/>
+      <c r="C1001" s="4"/>
+      <c r="D1001" s="4"/>
+      <c r="E1001" s="4"/>
+      <c r="F1001" s="15"/>
+      <c r="G1001" s="4"/>
+      <c r="H1001" s="4"/>
+      <c r="I1001" s="4"/>
+      <c r="J1001" s="4"/>
+      <c r="K1001" s="4"/>
+      <c r="L1001" s="4"/>
+      <c r="M1001" s="4"/>
+      <c r="N1001" s="4"/>
+      <c r="O1001" s="4"/>
+      <c r="P1001" s="4"/>
+      <c r="Q1001" s="4"/>
+      <c r="R1001" s="4"/>
+      <c r="S1001" s="4"/>
+      <c r="T1001" s="4"/>
+      <c r="U1001" s="4"/>
+      <c r="V1001" s="4"/>
+      <c r="W1001" s="4"/>
+      <c r="X1001" s="4"/>
+      <c r="Y1001" s="4"/>
+      <c r="Z1001" s="4"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="4"/>
+      <c r="B1002" s="4"/>
+      <c r="C1002" s="4"/>
+      <c r="D1002" s="4"/>
+      <c r="E1002" s="4"/>
+      <c r="F1002" s="15"/>
+      <c r="G1002" s="4"/>
+      <c r="H1002" s="4"/>
+      <c r="I1002" s="4"/>
+      <c r="J1002" s="4"/>
+      <c r="K1002" s="4"/>
+      <c r="L1002" s="4"/>
+      <c r="M1002" s="4"/>
+      <c r="N1002" s="4"/>
+      <c r="O1002" s="4"/>
+      <c r="P1002" s="4"/>
+      <c r="Q1002" s="4"/>
+      <c r="R1002" s="4"/>
+      <c r="S1002" s="4"/>
+      <c r="T1002" s="4"/>
+      <c r="U1002" s="4"/>
+      <c r="V1002" s="4"/>
+      <c r="W1002" s="4"/>
+      <c r="X1002" s="4"/>
+      <c r="Y1002" s="4"/>
+      <c r="Z1002" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F23"/>
